--- a/语音/传感器故障.xlsx
+++ b/语音/传感器故障.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="53">
   <si>
     <t>序号</t>
   </si>
@@ -131,6 +131,9 @@
     <t>已关闭水轮机调速器电调柜柜门</t>
   </si>
   <si>
+    <t>更换导叶传感器需要先停机。本次任务使用一键停机，详细内容请从手动停机任务学习</t>
+  </si>
+  <si>
     <t>断开1号水轮机导叶开度传感器的电源输入</t>
   </si>
   <si>
@@ -143,6 +146,15 @@
     <t>已更换1号水轮机导叶开度传感器</t>
   </si>
   <si>
+    <t>本次任务使用一键开机，详细内容请从手动开机任务学习</t>
+  </si>
+  <si>
+    <t>点击1号水轮机调速器电调柜面板故障及复归</t>
+  </si>
+  <si>
+    <t>已完成调速器电调柜故障复归操作</t>
+  </si>
+  <si>
     <t>使用调速器电调柜液晶显示屏进行传感器的定位试验，给定不同开度，观察传感器反馈的导叶开度与导叶开度指示标尺是否一致</t>
   </si>
   <si>
@@ -155,12 +167,6 @@
     <t>已完成传感器的定位试验</t>
   </si>
   <si>
-    <t>点击1号水轮机调速器电调柜面板故障及复归</t>
-  </si>
-  <si>
-    <t>已完成调速器电调柜故障复归操作</t>
-  </si>
-  <si>
     <t>再次检测1号水轮机调速器电调柜指示灯，A机报警熄灭,B机报警熄灭</t>
   </si>
   <si>
@@ -174,6 +180,9 @@
   </si>
   <si>
     <t>关闭1号水轮机调速器电调柜柜门</t>
+  </si>
+  <si>
+    <t>已关闭1号水轮机调速器电调柜柜门</t>
   </si>
   <si>
     <t>1号水轮机导叶传感器故障处理任务已完成</t>
@@ -1204,8 +1213,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.0083333333333" customWidth="1"/>
     <col min="2" max="2" width="31.8416666666667" customWidth="1"/>
@@ -1535,43 +1544,37 @@
       </c>
     </row>
     <row r="24" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
+      <c r="A24" s="2"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="C24" s="3"/>
       <c r="D24" s="3" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A25" s="2">
-        <v>24</v>
-      </c>
+      <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" ht="30.5" customHeight="1" spans="1:5">
       <c r="A26" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>2</v>
@@ -1579,12 +1582,12 @@
     </row>
     <row r="27" ht="30.5" customHeight="1" spans="1:5">
       <c r="A27" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>11</v>
@@ -1592,14 +1595,14 @@
     </row>
     <row r="28" ht="30.5" customHeight="1" spans="1:5">
       <c r="A28" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="3" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>2</v>
@@ -1607,40 +1610,34 @@
     </row>
     <row r="29" ht="30.5" customHeight="1" spans="1:5">
       <c r="A29" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="30" ht="63.5" customHeight="1" spans="1:5">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
+    <row r="30" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A30" s="2"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="3" t="s">
-        <v>38</v>
-      </c>
+      <c r="C30" s="3"/>
       <c r="D30" s="3" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" ht="47" customHeight="1" spans="1:5">
-      <c r="A31" s="2">
-        <v>30</v>
-      </c>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>8</v>
@@ -1648,119 +1645,189 @@
     </row>
     <row r="32" ht="30.5" customHeight="1" spans="1:5">
       <c r="A32" s="2">
+        <v>27</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" ht="30.5" customHeight="1" spans="1:7">
+      <c r="A33" s="2">
+        <v>28</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" ht="63.5" customHeight="1" spans="1:7">
+      <c r="A34" s="2">
+        <v>29</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" ht="47" customHeight="1" spans="1:7">
+      <c r="A35" s="2">
+        <v>30</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" ht="30.5" customHeight="1" spans="1:7">
+      <c r="A36" s="2">
         <v>31</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A33" s="2">
+      <c r="C36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" ht="30.5" customHeight="1" spans="1:7">
+      <c r="A37" s="2">
         <v>32</v>
-      </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" ht="47" customHeight="1" spans="1:5">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A37" s="2">
-        <v>36</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" ht="30.5" customHeight="1" spans="1:7">
+      <c r="A38" s="2">
+        <v>33</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" ht="47" customHeight="1" spans="1:7">
+      <c r="A39" s="2">
+        <v>34</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E39" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" ht="30.5" customHeight="1" spans="1:7">
+      <c r="A40" s="2">
+        <v>35</v>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" ht="30.5" customHeight="1" spans="1:7">
+      <c r="A41" s="2">
+        <v>36</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="38" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A38" s="2">
+    <row r="42" ht="30.5" customHeight="1" spans="1:7">
+      <c r="A42" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E38" s="2" t="s">
+      <c r="B42" s="2"/>
+      <c r="C42" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="39" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A39" s="2">
+    <row r="43" ht="30.5" customHeight="1" spans="1:7">
+      <c r="A43" s="2">
         <v>38</v>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E39" s="2" t="s">
+      <c r="B43" s="2"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:7">
+      <c r="D44" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:7">
+      <c r="D45" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="B2 D2:E2 B3:E16 B17 D17:E17 B18:C18 E18 B19:E39 A1:E1" numberStoredAsText="1"/>
+    <ignoredError sqref="B32:E33 B26:E29 B2 D2:E2 B3:E16 B17 D17:E17 B18:C18 E18 E42:E43 B42:C43 B19:E23 A1:E1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>